--- a/app/crates/freecell-app/assets/demo/demo.xlsx
+++ b/app/crates/freecell-app/assets/demo/demo.xlsx
@@ -2936,32 +2936,24 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:multiLvlStrRef>
+            <c:strRef>
               <c:f>'Quarterly P&amp;L'!$C$5:$F$5</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q4</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q3</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q2</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q1</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Q1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Q2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Q3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Q4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -3035,32 +3027,24 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:multiLvlStrRef>
+            <c:strRef>
               <c:f>'Quarterly P&amp;L'!$C$5:$F$5</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q4</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q3</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q2</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q1</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Q1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Q2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Q3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Q4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -3134,32 +3118,24 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:multiLvlStrRef>
+            <c:strRef>
               <c:f>'Quarterly P&amp;L'!$C$5:$F$5</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q4</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q3</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q2</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Q1</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Q1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Q2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Q3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Q4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -3360,15 +3336,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>364680</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>19080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -3395,15 +3371,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>290880</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>40320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -3425,15 +3401,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>399240</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>11880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>

--- a/app/crates/freecell-app/assets/demo/demo.xlsx
+++ b/app/crates/freecell-app/assets/demo/demo.xlsx
@@ -2129,126 +2129,6 @@
             </c:spPr>
           </c:dPt>
           <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -2264,10 +2144,10 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>

--- a/app/crates/freecell-app/assets/demo/demo.xlsx
+++ b/app/crates/freecell-app/assets/demo/demo.xlsx
@@ -294,30 +294,30 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Inter"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -325,7 +325,7 @@
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FF8D6E63"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -333,7 +333,7 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -341,14 +341,14 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF2B2B2B"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF2B2B2B"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -356,7 +356,7 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF3E2723"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -364,27 +364,27 @@
       <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Inter"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Inter"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Inter"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF5D4037"/>
-      <name val="Arial"/>
+      <name val="Inter"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -704,7 +704,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -712,7 +712,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:rPr>
               <a:t>Monthly Revenue Mix &amp; Growth</a:t>
             </a:r>
@@ -763,7 +763,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -901,7 +901,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1039,7 +1039,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1177,7 +1177,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1328,7 +1328,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1473,7 +1473,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -1503,7 +1503,7 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -1511,7 +1511,7 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Inter"/>
                   </a:rPr>
                   <a:t>Revenue (USD)</a:t>
                 </a:r>
@@ -1547,7 +1547,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -1584,7 +1584,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -1614,7 +1614,7 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -1622,7 +1622,7 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Inter"/>
                   </a:rPr>
                   <a:t>MoM Growth</a:t>
                 </a:r>
@@ -1658,7 +1658,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -1692,7 +1692,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Inter"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -1731,7 +1731,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1739,7 +1739,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:rPr>
               <a:t>Revenue by Product</a:t>
             </a:r>
@@ -1794,7 +1794,7 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1924,7 +1924,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -1974,7 +1974,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -2023,7 +2023,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -2031,7 +2031,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:rPr>
               <a:t>Share of Revenue by Region</a:t>
             </a:r>
@@ -2140,7 +2140,7 @@
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Inter"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -2164,7 +2164,7 @@
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Inter"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -2188,7 +2188,7 @@
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Inter"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -2212,7 +2212,7 @@
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Inter"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -2236,7 +2236,7 @@
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Inter"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -2258,7 +2258,7 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -2347,7 +2347,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Inter"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -2386,7 +2386,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -2394,7 +2394,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:rPr>
               <a:t>Channel Mix by Region</a:t>
             </a:r>
@@ -2445,7 +2445,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -2541,7 +2541,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -2637,7 +2637,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -2736,7 +2736,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -2786,7 +2786,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -2820,7 +2820,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Inter"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -2859,7 +2859,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -2867,7 +2867,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:rPr>
               <a:t>Revenue, Gross Profit &amp; Net Income by Quarter</a:t>
             </a:r>
@@ -2917,7 +2917,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -3008,7 +3008,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -3099,7 +3099,7 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Inter"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -3190,7 +3190,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -3240,7 +3240,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Inter"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -3274,7 +3274,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Inter"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -3510,12 +3510,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Inter" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Inter" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
